--- a/outputs/3002.xlsx
+++ b/outputs/3002.xlsx
@@ -137,28 +137,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -414,210 +418,210 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="3" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="3" t="n">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="4" t="n">
         <v>1941546513</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>90176278</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="3" t="n">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="4" t="n">
         <v>1941546513</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>90176278</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="3" t="n">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="4" t="n">
         <v>1941546513</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>90176279</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="3" t="n">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="4" t="n">
         <v>1941546514</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>90180157</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="3" t="n">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="4" t="n">
         <v>1941546514</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>90180157</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="3" t="n">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="4" t="n">
         <v>1941546514</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>90180157</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="3" t="n">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="4" t="n">
         <v>1941546630</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>90177950</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="3" t="n">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="4" t="n">
         <v>1941546630</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>90177951</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="3" t="n">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="4" t="n">
         <v>1941546625</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>90177943</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="3" t="n">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="4" t="n">
         <v>1941546626</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>90177944</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="3" t="n">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="4" t="n">
         <v>1941546627</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>90177945</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/3002.xlsx
+++ b/outputs/3002.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -89,19 +89,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -146,19 +139,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -415,64 +408,34 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="E3:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.66"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
       <c r="E5" s="4" t="n">
         <v>1941546513</v>
       </c>
@@ -484,10 +447,6 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
       <c r="E6" s="4" t="n">
         <v>1941546513</v>
       </c>
@@ -499,10 +458,6 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
       <c r="E7" s="4" t="n">
         <v>1941546513</v>
       </c>
@@ -510,14 +465,10 @@
         <v>90176279</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
       <c r="E8" s="4" t="n">
         <v>1941546514</v>
       </c>
@@ -525,14 +476,10 @@
         <v>90180157</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
       <c r="E9" s="4" t="n">
         <v>1941546514</v>
       </c>
@@ -540,14 +487,10 @@
         <v>90180157</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
       <c r="E10" s="4" t="n">
         <v>1941546514</v>
       </c>
@@ -555,73 +498,63 @@
         <v>90180157</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
       <c r="E11" s="4" t="n">
         <v>1941546630</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>90177950</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
       <c r="E12" s="4" t="n">
         <v>1941546630</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>90177951</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
       <c r="E13" s="4" t="n">
         <v>1941546625</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>90177943</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
       <c r="E14" s="4" t="n">
         <v>1941546626</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>90177944</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
       <c r="E15" s="4" t="n">
         <v>1941546627</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>90177945</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
